--- a/results/Int All Data 0.6/Rando_fi_explain.xlsx
+++ b/results/Int All Data 0.6/Rando_fi_explain.xlsx
@@ -1676,466 +1676,466 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.001289090605591546</v>
+        <v>-7.98485747847411e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>4.856130539314552e-05</v>
+        <v>-0.0002459791957930479</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005626247148922314</v>
+        <v>-0.0002829894729287674</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.083766783928747e-05</v>
+        <v>-0.0004125605128526787</v>
       </c>
       <c r="F3" t="n">
-        <v>-6.082844810589405e-05</v>
+        <v>-0.0004759330687900887</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0001321756649400374</v>
+        <v>-0.0001108536225374357</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0004313117538574529</v>
+        <v>-0.0001331862572277421</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0009116609450654679</v>
+        <v>-0.0001785553607697277</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0006501612607118558</v>
+        <v>-0.001830863246640007</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0005857595693253725</v>
+        <v>-0.0002623309279384645</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0002044527371206594</v>
+        <v>-0.0003561017800784327</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0005460676742317883</v>
+        <v>0.0006815027011972485</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0022925100358027</v>
+        <v>-0.001602388653845221</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0001022749879548324</v>
+        <v>0.0004380115818317421</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.00107142006354455</v>
+        <v>-0.0005983359051721271</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0006270061507424384</v>
+        <v>-6.702350141020831e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0004803002064330219</v>
+        <v>-0.0006210997730937695</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0006731311383117433</v>
+        <v>-0.0003438819353403167</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0002012213437261223</v>
+        <v>-0.0002646907709437451</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0002205147906773097</v>
+        <v>-0.0004615093300445393</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0008733514492906679</v>
+        <v>0.0002369473602707462</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0008646653475717127</v>
+        <v>0.0004831346857476093</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00112618543633179</v>
+        <v>0.001217381772881633</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.715065258838137e-06</v>
+        <v>-9.66295513750337e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0002009841216594699</v>
+        <v>0.00173065045923109</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0008599660520208141</v>
+        <v>0.0005007150138013649</v>
       </c>
       <c r="AB3" t="n">
-        <v>-2.38388343043483e-05</v>
+        <v>-0.0001035690607097939</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.0002711073721829982</v>
+        <v>-0.001222994914267614</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.002622013224284638</v>
+        <v>0.000508411675945618</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.003209247647621557</v>
+        <v>0.003069454372849743</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0001190638959801238</v>
+        <v>0.0009165629629176286</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.0008746468529300742</v>
+        <v>5.175200381082877e-05</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.0004176015116579456</v>
+        <v>-0.0001088571656333959</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0008123214064599548</v>
+        <v>0.0002922704168282474</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.0006643256998635262</v>
+        <v>0.001187257306929147</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.006765407784999731</v>
+        <v>0.01256111027555092</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.0004893139090853104</v>
+        <v>-0.0004092750066114569</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.002103983593215189</v>
+        <v>0.001872971080371449</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.0001071766095941907</v>
+        <v>-0.000316862372661586</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.0002684899740272729</v>
+        <v>0.0004801050835324316</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.0002235140969799687</v>
+        <v>0.0001623049490073902</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.0004049606017703012</v>
+        <v>0.0007568250000327969</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.003269504560076263</v>
+        <v>0.002923414234352928</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.0001126939373258684</v>
+        <v>-0.0001314736886565071</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.0005120575583504094</v>
+        <v>0.0006176062951960505</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.0004251795509920852</v>
+        <v>-0.0004961230196136335</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.0005508392802979723</v>
+        <v>-0.000487814849932987</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.0002464646190297026</v>
+        <v>-0.001279397786728809</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.0002151605092587383</v>
+        <v>-0.0001248000747502776</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.0008635306830475465</v>
+        <v>-0.0003486714217454545</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.001665034685069245</v>
+        <v>-0.0001074283652217534</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.0005484035216958061</v>
+        <v>-0.0004035969548715557</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.002667958050560294</v>
+        <v>-0.001598646974560083</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.0002684391561289589</v>
+        <v>-6.767094358365644e-05</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.0001330139678238218</v>
+        <v>-3.837926946368197e-05</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.001609545912515046</v>
+        <v>-0.0003605489428923591</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.001380294038537234</v>
+        <v>-0.001400779305071005</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.001558442546151219</v>
+        <v>0.0004845881874641233</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.0001673969207822501</v>
+        <v>-0.0001900373998929727</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.002036391229919635</v>
+        <v>0.0009925116897825357</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0.001029743436482726</v>
+        <v>-3.936269401100811e-05</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.0007794758567197635</v>
+        <v>-0.0005875091735165195</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.0001153120630126803</v>
+        <v>-0.0001806018997841485</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.00144155776645166</v>
+        <v>-0.0003566685434817319</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.0008752887822532373</v>
+        <v>-0.0002562890752668057</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0.001382981259235171</v>
+        <v>0.0002983980491517513</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.0003372297924977785</v>
+        <v>0.0003541849214565529</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0.0001533808272737115</v>
+        <v>0.001366840484290335</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.0004156146994545661</v>
+        <v>0.0001521224782063502</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0.0002443118533170086</v>
+        <v>-3.114770867098327e-05</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.0009157706123939024</v>
+        <v>1.19456537339557e-05</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.001460950619418218</v>
+        <v>-0.000313657671831915</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0.0008416327544446321</v>
+        <v>1.102573411261298e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.00150415457218083</v>
+        <v>-0.000436325179824556</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.001116778125370339</v>
+        <v>-0.0009375367275990223</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0.0009815187737946707</v>
+        <v>-0.0004909635145279334</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0.0003794697745393038</v>
+        <v>0.0009255393566886029</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.00101705767143105</v>
+        <v>-9.032754520962971e-05</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.0004803549083767288</v>
+        <v>-0.0003886867524815985</v>
       </c>
       <c r="CE3" t="n">
-        <v>-8.497119035341446e-05</v>
+        <v>-0.0007274363201014588</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.001350986073463535</v>
+        <v>0.0001712141602407935</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.0003655193285479796</v>
+        <v>0.0002831752806013965</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0005647535386808411</v>
+        <v>-0.0001488405879025567</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.0005795258634248591</v>
+        <v>0.0004357984734484455</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-4.828585224530002e-06</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.0004397368961912041</v>
+        <v>-0.0001566087352549761</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0.000365695411764475</v>
+        <v>-7.355396601548938e-05</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.0002541592908315848</v>
+        <v>-0.0002110296361704145</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.0003197864917890414</v>
+        <v>-2.22296275212508e-05</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.0001503432683654371</v>
+        <v>-7.515527988378625e-05</v>
       </c>
       <c r="CP3" t="n">
-        <v>-7.851578485805755e-05</v>
+        <v>0.0001076050646021376</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.0007476760373977276</v>
+        <v>0.0001985928982636131</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.0003438006498151958</v>
+        <v>-0.0003821050434384732</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0.0004027435099149812</v>
+        <v>-0.001061221404509023</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0.0009714255286998397</v>
+        <v>-0.0002638510752554735</v>
       </c>
       <c r="CU3" t="n">
-        <v>-7.339049216934513e-05</v>
+        <v>2.85638432905011e-05</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.0001253068350487774</v>
+        <v>-2.104389457995737e-05</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.0008540804069126619</v>
+        <v>-0.0005679804466263493</v>
       </c>
       <c r="CY3" t="n">
-        <v>-0.0001959454363519208</v>
+        <v>0.000100123329770988</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-3.381244997275213e-05</v>
+        <v>5.307855626326408e-06</v>
       </c>
       <c r="DA3" t="n">
-        <v>4.455909974393934e-05</v>
+        <v>1.550589936390012e-05</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.0002596089150649605</v>
+        <v>-0.0001230577158486956</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.0001258761253865403</v>
+        <v>-0.0004098413994086925</v>
       </c>
       <c r="DD3" t="n">
-        <v>-8.243255560667627e-05</v>
+        <v>-0.000257596775451987</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.0002770380291813912</v>
+        <v>-0.000294802706858448</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.0006384012595676036</v>
+        <v>-0.0004246834096305518</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.0005829611868915696</v>
+        <v>3.97085909853445e-05</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0.001103629909463332</v>
+        <v>-0.000690299259244459</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.0002895771778239353</v>
+        <v>-0.000241811842630304</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.0001103031724929904</v>
+        <v>0.0002127839595476766</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0.0007012805542537459</v>
+        <v>-0.0001671523434293976</v>
       </c>
       <c r="DL3" t="n">
-        <v>1.447320555260423e-05</v>
+        <v>-8.02414495321624e-05</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0.0001127648896236822</v>
+        <v>5.13064233877303e-05</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.001996955084906209</v>
+        <v>-0.002122828427538318</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.00173279078211136</v>
+        <v>-0.0008740826923385314</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.001470071513853822</v>
+        <v>-0.001270941123842428</v>
       </c>
       <c r="DQ3" t="n">
-        <v>1.006598484077137e-05</v>
+        <v>-7.069339581351587e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.091769396203381e-06</v>
+        <v>-9.061062057078683e-05</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.0003377262522832914</v>
+        <v>-0.0002636984916681973</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0.003955232262918771</v>
+        <v>-0.0007607567123223781</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0.001205699964952359</v>
+        <v>-0.0009633218151114519</v>
       </c>
       <c r="DV3" t="n">
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>3.695130765016041e-05</v>
+        <v>-4.689443430114126e-05</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.0004070671265375847</v>
+        <v>-0.0001909910593272024</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.001842158991588989</v>
+        <v>-0.002314158628165924</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.0001171954643476003</v>
+        <v>4.094035453855671e-05</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.0006615936638704967</v>
+        <v>7.367166472378449e-05</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.000602972372553533</v>
+        <v>-0.0005325432415120712</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.0002766662116627095</v>
+        <v>-0.0001107929843119315</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.0001133625735746224</v>
+        <v>0.0001924004441268346</v>
       </c>
       <c r="EE3" t="n">
-        <v>3.92927308447888e-05</v>
+        <v>-4.777830864787225e-05</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.0002096947772214564</v>
+        <v>-2.002534811490376e-05</v>
       </c>
       <c r="EG3" t="n">
-        <v>-8.287126431524071e-05</v>
+        <v>-8.546617437462434e-05</v>
       </c>
       <c r="EH3" t="n">
-        <v>-8.221600956758613e-05</v>
+        <v>-1.592356687898255e-05</v>
       </c>
       <c r="EI3" t="n">
-        <v>8.826185058072881e-06</v>
+        <v>-0.0002576472971977517</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-5.8993724719969e-05</v>
+        <v>7.15780334797178e-05</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.0001692978213743612</v>
+        <v>-0.0001535658450811539</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>-5.271481286241997e-06</v>
       </c>
       <c r="EM3" t="n">
-        <v>-8.425755286279979e-05</v>
+        <v>-9.679570131028603e-05</v>
       </c>
       <c r="EN3" t="n">
-        <v>8.183518534343848e-05</v>
+        <v>-2.695156816328703e-05</v>
       </c>
       <c r="EO3" t="n">
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>-2.892929732729033e-05</v>
+        <v>7.240842351608155e-05</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.0004514559027278108</v>
+        <v>-7.909781874123166e-05</v>
       </c>
       <c r="ER3" t="n">
-        <v>9.657170449060005e-06</v>
+        <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-7.900351817261564e-05</v>
+        <v>0</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.0003407041419955147</v>
+        <v>0.0003866360021945736</v>
       </c>
       <c r="EU3" t="n">
-        <v>-3.246765423013387e-05</v>
+        <v>-0.0004633939067798133</v>
       </c>
       <c r="EV3" t="n">
-        <v>-1.509466399744031e-05</v>
+        <v>2.167377441410823e-05</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0.0001630637460673379</v>
+        <v>4.077773952892982e-06</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.0001422167542843944</v>
+        <v>0.0001158757198525018</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.0002316488557924856</v>
+        <v>-3.661312867965893e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2145,466 +2145,466 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005561095445901091</v>
+        <v>0.001423524354556497</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0004878080556222219</v>
+        <v>0.000442571309139639</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001726995347922111</v>
+        <v>0.0006552141146103706</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001296967509272733</v>
+        <v>0.0009031822276909621</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0002189351913971755</v>
+        <v>0.0008880788929239722</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001691990008398684</v>
+        <v>0.002190787897202234</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001018074262321611</v>
+        <v>0.001263984404869258</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002665354767838404</v>
+        <v>0.001281195311626315</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002599953246738092</v>
+        <v>0.002874168038766751</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00154032372842772</v>
+        <v>0.0006484164261288458</v>
       </c>
       <c r="L4" t="n">
-        <v>0.000798861786001196</v>
+        <v>0.001273168028134405</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001601186754535248</v>
+        <v>0.001472221261625878</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002924842079443338</v>
+        <v>0.003822438470333267</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002862292813521205</v>
+        <v>0.001697896288710347</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002274775215605175</v>
+        <v>0.0008995209570239481</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.003217216515316168</v>
+        <v>0.003031826063079248</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001648126167844497</v>
+        <v>0.001856166464246478</v>
       </c>
       <c r="S4" t="n">
-        <v>0.004160461237511863</v>
+        <v>0.003009900001867541</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0005571193263064906</v>
+        <v>0.0005332907433827265</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001340841895090533</v>
+        <v>0.001219066033779924</v>
       </c>
       <c r="V4" t="n">
-        <v>0.003212680038127276</v>
+        <v>0.00209935909589722</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001917420677309896</v>
+        <v>0.001625809217240045</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005812500182086444</v>
+        <v>0.003329397706809722</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0002084241793796112</v>
+        <v>0.0002892741499210388</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001915800834163826</v>
+        <v>0.005643893175552176</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.003212200696746103</v>
+        <v>0.002736911566155003</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0003650865489534281</v>
+        <v>0.0004809513030527213</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0021937226056624</v>
+        <v>0.001509589723187753</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.01140500225734644</v>
+        <v>0.006540930956877191</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.008597603923438368</v>
+        <v>0.004873405647766877</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.001409228867462379</v>
+        <v>0.001738987211139024</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001678587258599139</v>
+        <v>0.0008924150342550612</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0007996706182498583</v>
+        <v>0.0009431163175809187</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.001842399688118583</v>
+        <v>0.001000109817735423</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.004997664006406292</v>
+        <v>0.002073302924866666</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01965229749839336</v>
+        <v>0.02229109262162775</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001190174377521971</v>
+        <v>0.0007813526065298972</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.00545328514579333</v>
+        <v>0.004129081628048773</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.002942066819521197</v>
+        <v>0.001333518737866027</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.003447416471465102</v>
+        <v>0.001438475906120984</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0009478764330251056</v>
+        <v>0.0003849910174093105</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.002272159975395378</v>
+        <v>0.001344114955828125</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.00805077678624941</v>
+        <v>0.004272738547336286</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.001347803915518649</v>
+        <v>0.0002664241016961814</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.002859434475893385</v>
+        <v>0.002624067460898939</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.001555354004385952</v>
+        <v>0.00164832297897169</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.001633429538959303</v>
+        <v>0.001090641431185519</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.002704525710113173</v>
+        <v>0.002863669899434367</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0008223868075332455</v>
+        <v>0.0002349464028280153</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.002202384908366011</v>
+        <v>0.001645520082459945</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.003137760634557262</v>
+        <v>0.000674969232482175</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.00309903613454007</v>
+        <v>0.001031572291372264</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.004769805892275408</v>
+        <v>0.003632693356197912</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0004904444667206978</v>
+        <v>0.0002972425497470021</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0004030544521901283</v>
+        <v>0.0001644985153330526</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.005392986087548041</v>
+        <v>0.002131866331229258</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.006244917713126374</v>
+        <v>0.005448384501552864</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.003507903264108553</v>
+        <v>0.001215844741253145</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0005217960120090244</v>
+        <v>0.0004341187024673656</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.005512746637424265</v>
+        <v>0.003474965810109497</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.002289514159957246</v>
+        <v>0.001722021323154952</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.00212284043226959</v>
+        <v>0.00195046147906763</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0004598798850996653</v>
+        <v>0.0006186443974730659</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.002115309487852085</v>
+        <v>0.001381184458412777</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.00240903629711948</v>
+        <v>0.001966976788219618</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.002090724071548703</v>
+        <v>0.001280070175537301</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.002289763742605295</v>
+        <v>0.002236738528044677</v>
       </c>
       <c r="BQ4" t="n">
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.002817088334097752</v>
+        <v>0.002321633301484171</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.00114879044621581</v>
+        <v>0.001245051607856011</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.0006011189832168351</v>
+        <v>0.0007381564652927126</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.002711858034077241</v>
+        <v>0.001510870720928112</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.001853253906029926</v>
+        <v>0.001046416356082944</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.002989979613870317</v>
+        <v>0.0008263285209047068</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.005642008240498296</v>
+        <v>0.002556725063016601</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.003978601294332305</v>
+        <v>0.003547533425561376</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.001787520232082157</v>
+        <v>0.00155843363223877</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.002179482838622195</v>
+        <v>0.001813520355663774</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.002346450768348699</v>
+        <v>0.0004169732597227036</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.003715957886331971</v>
+        <v>0.002380248347860316</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.001616803342530367</v>
+        <v>0.001986617250459648</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.002150256675257904</v>
+        <v>0.0007848801654231635</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.001390428538268895</v>
+        <v>0.001313481293034595</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.00219243081238127</v>
+        <v>0.0009757111006804404</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.001887448925619502</v>
+        <v>0.0009425120934941772</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>1.526932718575034e-05</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.001792625196831934</v>
+        <v>0.00103744629618389</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.001779943523011812</v>
+        <v>0.0008858933598188185</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.001357727308910734</v>
+        <v>0.0004772015554691061</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.001893478695009723</v>
+        <v>0.0002507966247506332</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.0003052517655562485</v>
+        <v>0.0006672873435585452</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0002107442231763653</v>
+        <v>0.0002867146680899379</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.002309772763422741</v>
+        <v>0.000705015306633988</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.001390676032398545</v>
+        <v>0.001788094828237927</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.002159104200451958</v>
+        <v>0.001666973782174557</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.001724760755433663</v>
+        <v>0.0009889990165924565</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0002455572946242438</v>
+        <v>9.482172450741126e-05</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.000312970409892561</v>
+        <v>5.115262434949097e-05</v>
       </c>
       <c r="CW4" t="n">
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.001161181269517365</v>
+        <v>0.0006081555992784409</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.001053911754237813</v>
+        <v>0.00185272184470598</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0001650184548766568</v>
+        <v>1.678491327053104e-05</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0002394275267652153</v>
+        <v>9.623179439650131e-05</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.001464994242844642</v>
+        <v>0.0005663843358144387</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.001058961806221447</v>
+        <v>0.0009198167657538463</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.000400270883603575</v>
+        <v>0.0004160146904759547</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.001116679230414053</v>
+        <v>0.000552452224902306</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.001576463466263917</v>
+        <v>0.0007836884379033192</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.001405654760780102</v>
+        <v>0.0005340671353758545</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.006420014652353745</v>
+        <v>0.003185189787783532</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.002424927280164309</v>
+        <v>0.001417855429602695</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.0007744165545542195</v>
+        <v>0.001033816867445317</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.001252229330531922</v>
+        <v>0.001148942723851797</v>
       </c>
       <c r="DL4" t="n">
-        <v>4.607530302045933e-05</v>
+        <v>0.0001571005209135455</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0005110581865236681</v>
+        <v>0.00121813228468073</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.004233140449700375</v>
+        <v>0.004956956908409642</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.005042113071142192</v>
+        <v>0.002513980529160551</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.006229600532659296</v>
+        <v>0.003260605737162458</v>
       </c>
       <c r="DQ4" t="n">
-        <v>5.986139177132744e-05</v>
+        <v>0.0002467674868987817</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0003860689855458332</v>
+        <v>0.0001960988928614193</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0008706453379165843</v>
+        <v>0.0008878359838342344</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.006823030134221222</v>
+        <v>0.003214901160009095</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.003824566173798997</v>
+        <v>0.001556338011777338</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.000134993256173336</v>
+        <v>0.0001093337045565596</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.0007559495191376834</v>
+        <v>0.0005752523828475248</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.003996661577220121</v>
+        <v>0.006908942405239886</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0002400799026724012</v>
+        <v>0.0002028350994926386</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.00102111830477689</v>
+        <v>0.0007554330769336092</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.002875611869609537</v>
+        <v>0.003246540240369371</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.002751969113694481</v>
+        <v>0.000820052798166746</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.0006919029930716499</v>
+        <v>0.001314412262163035</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0001242545249574846</v>
+        <v>0.0001510882780777961</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.0005198514210831401</v>
+        <v>0.0008511946336433201</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.0005497975021387618</v>
+        <v>0.0003686583621715732</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0002633584452759074</v>
+        <v>5.035473981160365e-05</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.001045930607884695</v>
+        <v>0.0008825783023218965</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0003600197751659689</v>
+        <v>0.0007546332146064142</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.0007823057807803784</v>
+        <v>0.0002620600552324231</v>
       </c>
       <c r="EL4" t="n">
-        <v>0</v>
+        <v>1.666988750747874e-05</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0001197211364389398</v>
+        <v>0.0001506125626449028</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0001977474660177555</v>
+        <v>8.199259209440937e-05</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>9.152530799210844e-05</v>
+        <v>0.0001879381686745962</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.0008798157743287588</v>
+        <v>0.0007107892155191484</v>
       </c>
       <c r="ER4" t="n">
-        <v>3.053865437150068e-05</v>
+        <v>0</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0002039454676176739</v>
+        <v>0</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.001715240596439552</v>
+        <v>0.001006706038116571</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.0003332134601817646</v>
+        <v>0.0006119857678783402</v>
       </c>
       <c r="EV4" t="n">
-        <v>3.358216216472883e-05</v>
+        <v>0.0001423392545630828</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.0006777539189492636</v>
+        <v>0.0007016169852808346</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0003934867968506596</v>
+        <v>0.0008822513881108122</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.0004519684573587881</v>
+        <v>0.0001132355389793085</v>
       </c>
     </row>
     <row r="5">
@@ -2614,466 +2614,466 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01313448456305597</v>
+        <v>-0.002825745682888581</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.001001581444385846</v>
+        <v>-0.000896151818661084</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.000933202357563867</v>
+        <v>-0.001620825147347682</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.002123142250530818</v>
+        <v>-0.001964636542239628</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0004345726702076003</v>
+        <v>-0.002214022140221428</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.00368369351669946</v>
+        <v>-0.004911591355599177</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.002424881391671041</v>
+        <v>-0.001815575728619145</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.007639979068550462</v>
+        <v>-0.002930402930402964</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.004866562009419118</v>
+        <v>-0.006777996070726855</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.004604918890633136</v>
+        <v>-0.001988487702773467</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.002441613588110425</v>
+        <v>-0.003929273084479323</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0006872852233676952</v>
+        <v>-0.0008600095556616782</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.008349705304518684</v>
+        <v>-0.01139489194499013</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.006115623506927859</v>
+        <v>-0.001337792642140423</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.007149805447470792</v>
+        <v>-0.002383268482490264</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.003453307392996097</v>
+        <v>-0.006369426751592388</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.004873387482083135</v>
+        <v>-0.00427308447937128</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0117216117216117</v>
+        <v>-0.007326007326007378</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.001255886970172648</v>
+        <v>-0.001317870321560399</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.002866698518872435</v>
+        <v>-0.003634577603143363</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.007740086000955581</v>
+        <v>-0.002341137123745773</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.005112279025322542</v>
+        <v>-0.0009077878643095727</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.007064364207221308</v>
+        <v>-0.003139717425431754</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.0004911591355599487</v>
+        <v>-0.0008434370057986528</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.002040816326530603</v>
+        <v>-0.002564102564102622</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.003558346415489244</v>
+        <v>-0.002062868369351612</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.0008492569002123473</v>
+        <v>-0.0008754863813229541</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.005876731963688498</v>
+        <v>-0.003774486383181985</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.01334379905808475</v>
+        <v>-0.01620825147347735</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.009105180533751922</v>
+        <v>-0.003767660910518067</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.001767304860088359</v>
+        <v>-0.0003927344133529687</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.004552590266875933</v>
+        <v>-0.001669941060903679</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.001517530088958618</v>
+        <v>-0.00201698513800429</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.001273885350318504</v>
+        <v>-0.0009554140127388866</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.005703819989534254</v>
+        <v>-0.002266736953083859</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.02323390894819465</v>
+        <v>-0.007662082514734736</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.002511773940345352</v>
+        <v>-0.001634159198734864</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.005703819989534254</v>
+        <v>-0.006827111984282852</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.005255613951266125</v>
+        <v>-0.003585461689587366</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.005447470817120603</v>
+        <v>-0.002145473574045043</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.002214022140221384</v>
+        <v>-0.000291828793774318</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.00353559483994268</v>
+        <v>-0.0008268482490272344</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.005756148613291445</v>
+        <v>-0.004133961276818465</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.003343949044586014</v>
+        <v>-0.0004911591355598821</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.008361204013377943</v>
+        <v>-0.0007367387033398564</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.003917821309125669</v>
+        <v>-0.0046916183447549</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.00172001911132349</v>
+        <v>-0.002547770700636976</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.006122448979591799</v>
+        <v>-0.008372579801151293</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.002406679764243647</v>
+        <v>-0.0006802721088435715</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.004862475442043257</v>
+        <v>-0.003045186640471431</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.00907787864309606</v>
+        <v>-0.001476014760147626</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.006832298136645964</v>
+        <v>-0.002616431187859813</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.01199235547061636</v>
+        <v>-0.009157509157509213</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.001080550098231847</v>
+        <v>-0.0005893909626718763</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.0007326007326007078</v>
+        <v>-0.0004418262150220897</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.003634577603143463</v>
+        <v>-0.005353634577603105</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.01118012422360248</v>
+        <v>-0.01414538310412571</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.01012900143334925</v>
+        <v>-0.0005733397037744447</v>
       </c>
       <c r="BH5" t="n">
+        <v>-0.001098901098901151</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-0.003870043000477741</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>-0.003976975405546856</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>-0.004029304029304071</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>-0.001845018450184532</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>-0.004006325777543518</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>-0.003872318158032473</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>-0.002319451765946268</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>-0.00280057943022699</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>-0.0008268482490272344</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>-0.001686874011597284</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>-0.001107011070110731</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>-0.003621438918396946</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-0.002510864316755223</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>-0.001303718010622945</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>-0.00598249027237352</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>-0.006760700389105034</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>-0.004405520169851418</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>-0.0002866698518872224</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>-0.0008691453404152894</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>-0.005838641188959682</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>-0.003978388998035309</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>-0.001021400778210113</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>-0.002635740643120743</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>-0.001605058365758749</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>-0.001317870321560377</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>-4.828585224530002e-05</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>-0.002055877701634179</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>-0.001786576533075868</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>-0.001220806794055229</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>-0.0006369426751592578</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>-0.001008492569002151</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>-0.000790722192936244</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>-0.00339702760084929</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>-0.0039008961518187</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>-0.002176220806794071</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>-5.271481286244218e-05</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>-0.0001592356687898478</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>-0.001496861419604112</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>-0.002653927813163515</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>-0.0001024065540194519</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>-0.001569858712715888</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>-0.002580028666985146</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>-0.00111464968152869</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>-0.001739588824459703</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>-0.00229335881509789</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>-0.000437743190661477</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>-0.006712062256809315</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>-0.003715498938428896</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>-0.001522593320235721</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>-0.001674515960230283</v>
+      </c>
+      <c r="DL5" t="n">
         <v>-0.000382226469182978</v>
       </c>
-      <c r="BI5" t="n">
-        <v>-0.004830148619957541</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>-0.005232862375719472</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>-0.004730052556139541</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>-0.0007849293563578885</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>-0.005756148613291445</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>-0.005648330058939088</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>-0.006354515050167242</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>-0.006450071667462975</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>-0.006384092098377781</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>-0.002266736953083792</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>-0.001167728237791965</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>-0.004343275771847155</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>-0.005303392259914008</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>-0.009225092250922462</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>-0.01486132914704342</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>-0.009366823652537914</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>-0.0040870488322718</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>-0.00477783086478738</v>
-      </c>
-      <c r="CC5" t="n">
-        <v>-0.007023411371237465</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>-0.008704883227176241</v>
-      </c>
-      <c r="CE5" t="n">
-        <v>-0.002675585284280946</v>
-      </c>
-      <c r="CF5" t="n">
-        <v>-0.004634495938843797</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>-0.003004744333157594</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>-0.0009942438513866557</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>-0.00247759620453345</v>
-      </c>
-      <c r="CJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>-0.003939688715953293</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>-0.003184713375796189</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>-0.001831501831501803</v>
-      </c>
-      <c r="CN5" t="n">
-        <v>-0.00151753008895863</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>-0.0001473477406680024</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>-0.0006211180124223392</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>-0.003087388801674485</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>-0.00350318471337584</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>-0.005494505494505464</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>-0.004638903531892447</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>-0.0004911591355599487</v>
-      </c>
-      <c r="CV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX5" t="n">
-        <v>-0.003426462836056921</v>
-      </c>
-      <c r="CY5" t="n">
-        <v>-0.002145473574044998</v>
-      </c>
-      <c r="CZ5" t="n">
-        <v>-0.0004300047778308502</v>
-      </c>
-      <c r="DA5" t="n">
-        <v>-0.0004186289900575346</v>
-      </c>
-      <c r="DB5" t="n">
-        <v>-0.001517530088958641</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>-0.001641718976339857</v>
-      </c>
-      <c r="DD5" t="n">
-        <v>-0.001146679407548989</v>
-      </c>
-      <c r="DE5" t="n">
-        <v>-0.0006279434850863019</v>
-      </c>
-      <c r="DF5" t="n">
-        <v>-0.004087048832271789</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>-0.0004911591355599599</v>
-      </c>
-      <c r="DH5" t="n">
-        <v>-0.009581712062256775</v>
-      </c>
-      <c r="DI5" t="n">
-        <v>-0.00525477707006371</v>
-      </c>
-      <c r="DJ5" t="n">
-        <v>-0.001799610894941628</v>
-      </c>
-      <c r="DK5" t="n">
-        <v>-0.00272108843537413</v>
-      </c>
-      <c r="DL5" t="n">
-        <v>-4.911591355599709e-05</v>
-      </c>
       <c r="DM5" t="n">
-        <v>-0.001061571125265426</v>
+        <v>-0.002003162888771781</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0.008657587548638102</v>
+        <v>-0.01467889908256885</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.007822308063737293</v>
+        <v>-0.006712062256809315</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0.0140127388535032</v>
+        <v>-0.01008492569002126</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-9.727626459143934e-05</v>
+        <v>-0.000764452938365956</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.0004246284501061903</v>
+        <v>-0.0005120327700972593</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.002600849256900239</v>
+        <v>-0.002707006369426779</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.02117834394904462</v>
+        <v>-0.008811040339702803</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0.008463035019455223</v>
+        <v>-0.00398089171974525</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-4.911591355599709e-05</v>
+        <v>-0.00031847133757964</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.002266736953083792</v>
+        <v>-0.001385570950788295</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0.009776264591439654</v>
+        <v>-0.02013520038628686</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0.0001055408970976224</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.003025477707006408</v>
+        <v>-0.0007295719844357951</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.006857976653696474</v>
+        <v>-0.00739299610894939</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0.004140127388535064</v>
+        <v>-0.002070063694267554</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0.0006876227897838927</v>
+        <v>-0.002259332023575589</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0.0004777830864787225</v>
       </c>
       <c r="EF5" t="n">
+        <v>-0.001080550098231781</v>
+      </c>
+      <c r="EG5" t="n">
         <v>-0.0006322957198443557</v>
       </c>
-      <c r="EG5" t="n">
-        <v>-0.00125588697017267</v>
-      </c>
       <c r="EH5" t="n">
-        <v>-0.0006688963210702114</v>
+        <v>-0.0001592356687898255</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.00151753008895863</v>
+        <v>-0.00141050583657587</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.0007782101167315147</v>
+        <v>-0.001326129666011722</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0.001624462494027745</v>
+        <v>-0.0007907221929362662</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>-5.271481286241997e-05</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0.0003438113948919796</v>
+        <v>-0.0003690036900369287</v>
       </c>
       <c r="EN5" t="n">
-        <v>-4.909180166912108e-05</v>
+        <v>-0.0002123142250531007</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.0002454590083456054</v>
+        <v>-4.863813229571967e-05</v>
       </c>
       <c r="EQ5" t="n">
-        <v>-0.002529182879377423</v>
+        <v>-0.001021400778210113</v>
       </c>
       <c r="ER5" t="n">
         <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.0005733397037744669</v>
+        <v>0</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0.001098901098901117</v>
+        <v>-0.0003929273084478879</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.0006802721088434938</v>
+        <v>-0.00152259332023571</v>
       </c>
       <c r="EV5" t="n">
-        <v>-9.823182711199419e-05</v>
+        <v>-0.000196463654223944</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0.001963906581741004</v>
+        <v>-0.0008349705304518285</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.0008434370057986196</v>
+        <v>-0.0009727626459143934</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.001215953307392992</v>
+        <v>-0.0002123142250531007</v>
       </c>
     </row>
     <row r="6">
@@ -3083,442 +3083,442 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.002945712582082818</v>
+        <v>-0.000761416105432916</v>
       </c>
       <c r="C6" t="n">
-        <v>-3.683693516700614e-05</v>
+        <v>-0.0006663459428436712</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.000145914396887159</v>
+        <v>-0.0005925529445540922</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0007912769885522475</v>
+        <v>-0.0006709552966801591</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0001542180026754464</v>
+        <v>-0.0007299568117881655</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0001345994798781641</v>
+        <v>-0.0008274153357439862</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0003142983896574164</v>
+        <v>-0.000727422409987355</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.00158692482908708</v>
+        <v>-0.000383868335459514</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.002113179283920269</v>
+        <v>-0.004321745729231255</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0006214706198662406</v>
+        <v>-0.0001226703385748984</v>
       </c>
       <c r="L6" t="n">
-        <v>-7.849293563578775e-05</v>
+        <v>-5.275653962721616e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0003151410196039845</v>
+        <v>-6.635485357078252e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.003679175331784681</v>
+        <v>-0.002341661983184609</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0008839779405169473</v>
+        <v>-0.0006016096613436993</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.001302046690368341</v>
+        <v>-0.0008591374369626815</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.001945687977472974</v>
+        <v>-0.001028815112877837</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.0005726477744150693</v>
+        <v>-0.001151193481700133</v>
       </c>
       <c r="S6" t="n">
-        <v>6.035731530662225e-05</v>
+        <v>-0.001710701520203956</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.000464494427385595</v>
+        <v>-0.0003778681481571983</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0006064166424334689</v>
+        <v>-0.0004897409427704279</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0005139694254085198</v>
+        <v>-0.0009027608586342718</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.000680493502077037</v>
+        <v>-0.0003345368742774746</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.001070492579879234</v>
+        <v>-0.0005335398038659345</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0006991850962824926</v>
+        <v>-0.0005330516235957317</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.0003271384267914401</v>
+        <v>-0.0005390577741854695</v>
       </c>
       <c r="AB6" t="n">
-        <v>-8.574533339531232e-05</v>
+        <v>-0.000236809069121624</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.0004736181382432342</v>
+        <v>-0.002358274342820094</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0001647770633283863</v>
+        <v>4.029009879648049e-05</v>
       </c>
       <c r="AE6" t="n">
-        <v>9.288747346071491e-05</v>
+        <v>1.979508131820794e-05</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.0004738540321038681</v>
+        <v>-0.0002183696952176878</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0009739553612207463</v>
+        <v>-0.000346797498469964</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.001016033249504469</v>
+        <v>-0.0006198719767326139</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.0001177394034536733</v>
+        <v>-0.0003106289947177376</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.001465752550104687</v>
+        <v>0.0001939493584049712</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.002715628584086196</v>
+        <v>0.002672422894070503</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.001307608111517452</v>
+        <v>-0.0009076588605307634</v>
       </c>
       <c r="AM6" t="n">
-        <v>8.960573476702039e-05</v>
+        <v>0.001303057033274924</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.00067420632352658</v>
+        <v>-0.0007206231386405111</v>
       </c>
       <c r="AO6" t="n">
+        <v>3.681885125184081e-05</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-3.924646781792717e-05</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.0002445419911415753</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.979508131819965e-05</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-0.0003612530089569715</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-0.0006168796140745336</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0.0006728232189973455</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-0.001143682244275873</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-0.0009121350802609563</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-8.561844749594706e-05</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-0.0006650753785366892</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-0.000291809638488752</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-0.0005535472618201699</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-0.003189315722784089</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-0.0001704708787203635</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-4.89083982283145e-05</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-0.0008616426370449486</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-0.0008218368530743202</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-6.621998521852412e-05</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-0.0001828710355904317</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-0.001693570010219858</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-0.0004299717589425933</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-0.001553588397804648</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-9.189078481221802e-05</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-0.000622622703806064</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>-0.0005024335561987808</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-0.0002758694762269448</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>-3.840245775728613e-05</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>-0.0001197419808299682</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-0.0007674839274383922</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>-0.0004106088785342937</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-0.0003777641111956803</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>-0.0005237408730050741</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>-0.0004818521392013553</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>-0.00122932336673384</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>-0.00313625516390226</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>-0.0005947893116315134</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>-0.0002936922776548362</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>-0.0004211398002187144</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>-0.002303674463493552</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>-3.68369351669895e-05</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>-7.849293563582104e-05</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>-0.0006722403333405458</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>-5.026563738295686e-05</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>-0.0004804456797611933</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>-0.000444993428032997</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>-0.0004529845954847844</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>-3.621438918397502e-05</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>-0.0005117753969406613</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>-9.799293648183048e-05</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>-0.0007474156226072115</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>-0.002552088246840364</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>-0.0005495444164616031</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>-0.001158181126552274</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>-0.0006430468693861769</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>-7.907221929362996e-05</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>-0.0005706841828465537</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>-0.0005543870536650785</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>-0.0003449073500375932</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>-0.0007148731614154968</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>-0.0002438171420690333</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>-0.002252088082681897</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>-0.0002436437415350628</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>-0.0001829127623552085</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>-0.0006386222665728941</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>-3.647859922178975e-05</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>-0.0002577319587628857</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>-0.00192775741127062</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>-0.0006725322140362311</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>-0.00136154956867296</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>-0.0001841846758349558</v>
+      </c>
+      <c r="DS6" t="n">
         <v>-0.0001472754050073632</v>
       </c>
-      <c r="AP6" t="n">
-        <v>-0.0001075011944577292</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>-0.0002577319587628857</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>-0.00155487062216966</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>-0.0003555125873892062</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>-7.68049155145889e-05</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>-0.0008656720895119346</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>-0.0001104565537555224</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>-0.001080965463403255</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>-0.0002119504816522316</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>-0.001710667597887241</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-0.00262411799604701</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>-0.0002411040904555933</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>-0.003834221799540352</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>-0.0005439148122582977</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>-0.0004261507443042989</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>-0.0006695530675808691</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>-0.005539722465443361</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>-0.001792682621019992</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>-3.681885125184081e-05</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>-0.001595546804397152</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>-0.002420161413712299</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>-0.002184328582333306</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>-0.0004659691411447342</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>-0.001948118850858191</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>-0.001090395816330517</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>-0.001666912477877006</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>-0.0001448575567358418</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>-0.001203793774319062</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>-0.001058237713377117</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>-0.0007285547049906138</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>-0.003398823375520171</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>-0.002302790316964847</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>-0.0002282604590986504</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>-0.0009007688859773212</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>-0.0007627344314680151</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>-0.002110494595373033</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>-0.001397945439774203</v>
-      </c>
-      <c r="CC6" t="n">
-        <v>-0.0007943210208357365</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>3.924646781790775e-05</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>-0.0006614299472497698</v>
-      </c>
-      <c r="CF6" t="n">
-        <v>-0.002889136887274232</v>
-      </c>
-      <c r="CG6" t="n">
-        <v>-0.0003163867505523166</v>
-      </c>
-      <c r="CH6" t="n">
-        <v>-0.0001226145008809687</v>
-      </c>
-      <c r="CI6" t="n">
-        <v>1.227295041728027e-05</v>
-      </c>
-      <c r="CJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK6" t="n">
-        <v>-0.000244518191334736</v>
-      </c>
-      <c r="CL6" t="n">
-        <v>-0.001577252974768512</v>
-      </c>
-      <c r="CM6" t="n">
-        <v>-0.0001105108055009851</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>-3.681885125184081e-05</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>-0.0001094357976653693</v>
-      </c>
-      <c r="CP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ6" t="n">
-        <v>1.280081925243148e-05</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>-0.00103915326005351</v>
-      </c>
-      <c r="CS6" t="n">
-        <v>-0.0001345994798781614</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>-0.002021805687856548</v>
-      </c>
-      <c r="CU6" t="n">
-        <v>-7.907221929361329e-05</v>
-      </c>
-      <c r="CV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX6" t="n">
-        <v>-0.001301787730408649</v>
-      </c>
-      <c r="CY6" t="n">
-        <v>-0.0006467555190830642</v>
-      </c>
-      <c r="CZ6" t="n">
-        <v>-3.980891719745638e-05</v>
-      </c>
-      <c r="DA6" t="n">
-        <v>-1.665334536937735e-17</v>
-      </c>
-      <c r="DB6" t="n">
-        <v>-0.0001976805482340332</v>
-      </c>
-      <c r="DC6" t="n">
-        <v>-0.0003572395734708023</v>
-      </c>
-      <c r="DD6" t="n">
-        <v>-3.924646781789388e-05</v>
-      </c>
-      <c r="DE6" t="n">
-        <v>-0.0001990445859872819</v>
-      </c>
-      <c r="DF6" t="n">
-        <v>-0.0003883970994511626</v>
-      </c>
-      <c r="DG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH6" t="n">
-        <v>-0.005239649297087165</v>
-      </c>
-      <c r="DI6" t="n">
-        <v>3.621438918397779e-05</v>
-      </c>
-      <c r="DJ6" t="n">
-        <v>-0.0004417356397422384</v>
-      </c>
-      <c r="DK6" t="n">
-        <v>-0.001282953551184984</v>
-      </c>
-      <c r="DL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM6" t="n">
-        <v>-0.0003258445691967759</v>
-      </c>
-      <c r="DN6" t="n">
-        <v>-0.00344480086442949</v>
-      </c>
-      <c r="DO6" t="n">
-        <v>-0.006908189587515582</v>
-      </c>
-      <c r="DP6" t="n">
-        <v>-0.003225262397468137</v>
-      </c>
-      <c r="DQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR6" t="n">
-        <v>-0.000145914396887159</v>
-      </c>
-      <c r="DS6" t="n">
-        <v>-0.0004421643109047801</v>
-      </c>
       <c r="DT6" t="n">
-        <v>-0.005614520055513836</v>
+        <v>-0.001031532754168491</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0.002933536078324622</v>
+        <v>-0.002056020363538366</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>-8.561844749594706e-05</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.0005527342820036613</v>
+        <v>-0.0004709431047444479</v>
       </c>
       <c r="DY6" t="n">
-        <v>-0.003591269149891635</v>
+        <v>-0.0003538497703958476</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-8.694350939979779e-05</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.000635564756147819</v>
+        <v>-0.0003617632341416487</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.001419669508342058</v>
+        <v>-0.001508035901998092</v>
       </c>
       <c r="EC6" t="n">
-        <v>-0.00013662086563411</v>
+        <v>-0.0001840942562592041</v>
       </c>
       <c r="ED6" t="n">
-        <v>-7.242877836793337e-05</v>
+        <v>-0.0001544420604263491</v>
       </c>
       <c r="EE6" t="n">
         <v>0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0.0003096454362488232</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.000258407704977548</v>
+        <v>-0.0003139717425432009</v>
       </c>
       <c r="EH6" t="n">
-        <v>-7.367387033399564e-05</v>
+        <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.000610176638941487</v>
+        <v>-0.001046846512596172</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-8.484616618742447e-05</v>
+        <v>-3.957783641160839e-05</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.0003711861504420461</v>
+        <v>-0.0002288311400383131</v>
       </c>
       <c r="EL6" t="n">
         <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0.0001059752408261172</v>
+        <v>-0.0001713952018637554</v>
       </c>
       <c r="EN6" t="n">
-        <v>0</v>
+        <v>-3.68369351669895e-05</v>
       </c>
       <c r="EO6" t="n">
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-3.953610964680664e-05</v>
+        <v>0</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0.0002604492171578487</v>
+        <v>-0.000552535943589727</v>
       </c>
       <c r="ER6" t="n">
         <v>0</v>
@@ -3527,22 +3527,22 @@
         <v>0</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.0002113235643762784</v>
+        <v>-7.166746297179171e-05</v>
       </c>
       <c r="EU6" t="n">
-        <v>-9.821977116857282e-05</v>
+        <v>-0.0008603174654815582</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0.0002067825708829462</v>
+        <v>-0.0003236254748409051</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0.0003184713375796427</v>
+        <v>-0.0001801537771954576</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.0002605577206487908</v>
+        <v>-9.215437523293069e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3552,295 +3552,295 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0002454590083456054</v>
+        <v>0.0002564949489846813</v>
       </c>
       <c r="C7" t="n">
-        <v>7.242877836795003e-05</v>
+        <v>-2.414292612266666e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0.000184837307294683</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-7.295719844357951e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-0.0001527933753268984</v>
       </c>
       <c r="G7" t="n">
-        <v>2.560163850486297e-05</v>
+        <v>-5.277044854881119e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0001237852418431051</v>
+        <v>-0.0001227295041728083</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0003927344133529687</v>
+        <v>-7.680491551458335e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0003108543603845326</v>
+        <v>-0.0003394596780992909</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.653927813165424e-05</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2.454590083456609e-05</v>
+        <v>-2.454590083456054e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.0002257683406431343</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.001276640514392974</v>
+        <v>-7.826362789681852e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0001024065540194519</v>
+        <v>-2.560163850486297e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.0004089071132927336</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0004151113164646058</v>
+        <v>0.0002210095550585378</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.0001024065540194519</v>
+        <v>-0.0007158625769882188</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0003906929011726623</v>
+        <v>2.747691775840111e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0001032151454162578</v>
+        <v>-2.388915432394168e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>-7.242877836792783e-05</v>
+        <v>-7.242877836796113e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>7.52561135477392e-05</v>
+        <v>-7.68049155145889e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0001527099217972894</v>
+        <v>3.212710201205837e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0001207146306132556</v>
+        <v>0.0006506217135904102</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.653927813161539e-05</v>
+        <v>-0.0003646916252244226</v>
       </c>
       <c r="AA7" t="n">
-        <v>-1.665334536937735e-17</v>
+        <v>-3.33066907387547e-17</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.560163850486297e-05</v>
+        <v>-9.622541974979026e-05</v>
       </c>
       <c r="AC7" t="n">
-        <v>-4.828585224528892e-05</v>
+        <v>-0.0006493035741471642</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0005622873723278854</v>
+        <v>0.001886907497912799</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0005339090263967005</v>
+        <v>0.001667540630340492</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>4.626446648930971e-05</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.0001945525291828787</v>
+        <v>4.85396240440139e-05</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.0003683693516699504</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0003154432998213497</v>
+        <v>0.0001024065540194741</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-9.657170449056673e-05</v>
+        <v>0.0005991517215063636</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.004257981951314893</v>
+        <v>0.003648168228433291</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.0003104978283913318</v>
+        <v>-0.0003285448086814524</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.001129388725088787</v>
+        <v>0.002090029928923132</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0001792114695340408</v>
+        <v>-0.0001715944711552231</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0002472641107553519</v>
+        <v>0.0002262400196363368</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>5.109723490961393e-05</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0003253740885758971</v>
+        <v>5.090330726575942e-05</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0001792114695340463</v>
+        <v>0.002493817754669636</v>
       </c>
       <c r="AS7" t="n">
-        <v>-2.45579567780152e-05</v>
+        <v>-7.547702594352667e-05</v>
       </c>
       <c r="AT7" t="n">
-        <v>9.657170449060559e-05</v>
+        <v>-0.0001500467131402505</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.0001706123817061755</v>
+        <v>7.166746297183612e-05</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.000131787032156061</v>
+        <v>-0.0001567441741073427</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>-0.0001940241091072547</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>-0.0003634869994317169</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-9.818360333824216e-05</v>
+        <v>-0.0001227295041728027</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0002414292612264779</v>
+        <v>-7.388749075015188e-05</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.0007902894783931192</v>
+        <v>4.712156213727558e-05</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0.0001527099217972949</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-9.555661729575004e-05</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0001690004828585501</v>
+        <v>-5.412070177416294e-05</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.0003404669260700377</v>
+        <v>2.816891202784277e-05</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.0002569306233863644</v>
+        <v>0.0001471969692441677</v>
       </c>
       <c r="BH7" t="n">
-        <v>5.015959528284486e-05</v>
+        <v>-0.0001018622502179323</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.0002048131080389037</v>
+        <v>0.001550728264369905</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-0.0001452098367862975</v>
+        <v>0.0001525540933589031</v>
       </c>
       <c r="BK7" t="n">
-        <v>-7.283175307983835e-05</v>
+        <v>-0.000338806915140899</v>
       </c>
       <c r="BL7" t="n">
         <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.0004360235433657933</v>
+        <v>0.0001754999527216139</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0.0001960608337455816</v>
+        <v>-7.523774397550364e-05</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.0006110822318882769</v>
+        <v>0.0002211399421977456</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0001254430478103086</v>
+        <v>9.750309927814005e-05</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0003950390922556723</v>
+        <v>0.0006572544038309869</v>
       </c>
       <c r="BS7" t="n">
         <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-7.907221929361885e-05</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0.0005836575875486361</v>
+        <v>0.000168936564448513</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.000622989034079735</v>
+        <v>2.220446049250313e-17</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>-2.635740643121553e-05</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0002048131080389037</v>
+        <v>-7.574917784428648e-05</v>
       </c>
       <c r="BZ7" t="n">
-        <v>5.120327700972593e-05</v>
+        <v>2.243442549395568e-05</v>
       </c>
       <c r="CA7" t="n">
-        <v>-2.616431187859592e-05</v>
+        <v>-0.0001749885188528311</v>
       </c>
       <c r="CB7" t="n">
+        <v>0.0002006675500329014</v>
+      </c>
+      <c r="CC7" t="n">
         <v>-2.454590083456054e-05</v>
       </c>
-      <c r="CC7" t="n">
-        <v>-7.363770250368162e-05</v>
-      </c>
       <c r="CD7" t="n">
-        <v>0.000783364432963779</v>
+        <v>-7.849293563580995e-05</v>
       </c>
       <c r="CE7" t="n">
-        <v>-5.271481286239221e-05</v>
+        <v>-2.454590083454944e-05</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.0004847960627302583</v>
+        <v>4.828585224527227e-05</v>
       </c>
       <c r="CG7" t="n">
-        <v>-4.909180166912108e-05</v>
+        <v>4.911591355600819e-05</v>
       </c>
       <c r="CH7" t="n">
-        <v>0</v>
+        <v>-0.0001846965699208392</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.0002443466859909261</v>
+        <v>0.0004892480105188445</v>
       </c>
       <c r="CJ7" t="n">
         <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>0</v>
+        <v>-2.454590083456054e-05</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0.0002209131075110449</v>
+        <v>0.0001582278921168301</v>
       </c>
       <c r="CM7" t="n">
-        <v>0</v>
+        <v>-2.454590083456054e-05</v>
       </c>
       <c r="CN7" t="n">
         <v>0</v>
       </c>
       <c r="CO7" t="n">
-        <v>7.68049155145889e-05</v>
+        <v>-2.635740643120998e-05</v>
       </c>
       <c r="CP7" t="n">
         <v>0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0003402179116932691</v>
+        <v>-2.616431187860147e-05</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.0001024065540194519</v>
+        <v>-0.0001011239816624487</v>
       </c>
       <c r="CS7" t="n">
-        <v>0</v>
+        <v>-0.0003906929011726623</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0.0001248409795134076</v>
+        <v>-2.560163850486852e-05</v>
       </c>
       <c r="CU7" t="n">
         <v>0</v>
@@ -3852,10 +3852,10 @@
         <v>0</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0.000390919735859363</v>
+        <v>-0.0003656933309647004</v>
       </c>
       <c r="CY7" t="n">
-        <v>-0.0002686914161589227</v>
+        <v>-0.0001484795416011653</v>
       </c>
       <c r="CZ7" t="n">
         <v>0</v>
@@ -3867,46 +3867,46 @@
         <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>-9.818360333824216e-05</v>
+        <v>-0.0004074490008717291</v>
       </c>
       <c r="DD7" t="n">
-        <v>0</v>
+        <v>-2.431906614785984e-05</v>
       </c>
       <c r="DE7" t="n">
-        <v>0</v>
+        <v>-0.0001048781599102044</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.0001207146306132167</v>
+        <v>-0.0001468699594076861</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.0002399066304342168</v>
+        <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.000813181940551405</v>
+        <v>-0.0002564949489846757</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.0002240803205219521</v>
+        <v>2.431906614785984e-05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0</v>
+        <v>-7.907221929362996e-05</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0.0003113203216072946</v>
+        <v>-0.0001564720222065885</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-5.551115123125783e-18</v>
+        <v>0</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0.001836142072760916</v>
+        <v>1.125346747449235e-06</v>
       </c>
       <c r="DO7" t="n">
-        <v>-7.363770250368162e-05</v>
+        <v>-0.0001335864818092558</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0.000520898434315692</v>
+        <v>-0.0005841324189193253</v>
       </c>
       <c r="DQ7" t="n">
         <v>0</v>
@@ -3918,10 +3918,10 @@
         <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>-0.0005375919700888355</v>
+        <v>-3.654534992808547e-06</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0.001062287480933838</v>
+        <v>-0.0004460491657032994</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
@@ -3930,22 +3930,22 @@
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.0002786107875453414</v>
+        <v>-2.635740643120998e-05</v>
       </c>
       <c r="DY7" t="n">
-        <v>-0.0008765782788782983</v>
+        <v>7.849293563577664e-05</v>
       </c>
       <c r="DZ7" t="n">
         <v>0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.0002654559073795526</v>
+        <v>-7.86801947681548e-05</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.110223024625157e-17</v>
+        <v>-0.0002773950728722829</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>9.859309024652928e-05</v>
       </c>
       <c r="ED7" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="EF7" t="n">
-        <v>4.777830864787225e-05</v>
+        <v>-4.777830864786669e-05</v>
       </c>
       <c r="EG7" t="n">
         <v>0</v>
@@ -3963,19 +3963,19 @@
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>-4.828585224528892e-05</v>
+        <v>0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-2.616431187858481e-05</v>
+        <v>0</v>
       </c>
       <c r="EK7" t="n">
-        <v>-5.232862375719183e-05</v>
+        <v>-0.0001247460192350724</v>
       </c>
       <c r="EL7" t="n">
         <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-2.414292612264446e-05</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>0</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-5.307855626327518e-05</v>
+        <v>-5.277044854881119e-05</v>
       </c>
       <c r="ER7" t="n">
         <v>0</v>
@@ -3999,19 +3999,19 @@
         <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>1.110223024625157e-17</v>
+        <v>-0.0001054296257248399</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0</v>
+        <v>-0.0001267256201673117</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-5.232862375720293e-05</v>
       </c>
       <c r="EY7" t="n">
-        <v>0</v>
+        <v>-2.454590083456054e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4021,410 +4021,410 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0006100631869700695</v>
+        <v>0.0008361017963672335</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0003238170763944281</v>
+        <v>8.326672684688675e-18</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004609300766388907</v>
+        <v>0.0001554271801922524</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0002867967377866321</v>
+        <v>7.915567282321679e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-2.775557561562892e-18</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0006132284208652083</v>
+        <v>0.0007818404262495832</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0001473477406679496</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006649132449353529</v>
+        <v>7.367387033401228e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>9.795676865154146e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0001274803236891636</v>
+        <v>4.815896634593752e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.000100694069838525</v>
+        <v>0.0001720364880422348</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0006721138639957964</v>
+        <v>0.0009548610006345215</v>
       </c>
       <c r="N8" t="n">
-        <v>-8.960573476702039e-05</v>
+        <v>0.0002518212401673075</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0007299198516363459</v>
+        <v>0.0005796007813666237</v>
       </c>
       <c r="P8" t="n">
-        <v>8.68525735495812e-05</v>
+        <v>-1.583606505453636e-06</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002200974345286047</v>
+        <v>0.001055413849988371</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0004133360545010178</v>
+        <v>-4.909180166912108e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001070437934779397</v>
+        <v>0.001984183248586227</v>
       </c>
       <c r="T8" t="n">
-        <v>3.840245775729445e-05</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0001951938153613802</v>
+        <v>0.0002122371981244514</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0002322752229295927</v>
+        <v>0.0007073053462088418</v>
       </c>
       <c r="W8" t="n">
-        <v>7.68049155145889e-05</v>
+        <v>0.0004561587618377328</v>
       </c>
       <c r="X8" t="n">
-        <v>0.002576743300569248</v>
+        <v>0.001594929403040987</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.840245775729445e-05</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0001360581922603854</v>
+        <v>0.001447971105290852</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0006199224775863099</v>
+        <v>0.0002172863351037835</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001865218728252654</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.001170697125909759</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.004686689757061629</v>
+        <v>0.004305215611620158</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.00334784120234799</v>
+        <v>0.006819111827715754</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0008628864981859968</v>
+        <v>0.001717743075994002</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0001194267515923358</v>
+        <v>0.0004506966451388594</v>
       </c>
       <c r="AH8" t="n">
-        <v>7.68049155145889e-05</v>
+        <v>0.0002767527675276548</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.001012094636532146</v>
+        <v>0.001074800562520742</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0005467401460085037</v>
+        <v>0.002424016491110364</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.005826172096804055</v>
+        <v>0.007051445628196023</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>0.0002303719344392913</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.003036159131046562</v>
+        <v>0.003409644968870351</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.001302541574760183</v>
+        <v>0.0005512382312763186</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.00132972732846969</v>
+        <v>0.001173853247704215</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0002800400024194627</v>
+        <v>0.0003031379918020604</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.001345192575625398</v>
+        <v>0.001891224717311699</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.007696904917882045</v>
+        <v>0.006408690428006434</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.0005733641678342449</v>
+        <v>-8.326672684688674e-18</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0004606202741791493</v>
+        <v>0.0004100267693730397</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.0001152073732718833</v>
+        <v>0.0003507905937950001</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0007286344518583066</v>
+        <v>0.0001348298716488616</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.001401893542842752</v>
+        <v>-5.001146338904361e-05</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0004345726702076752</v>
+        <v>-0.0001158910705454708</v>
       </c>
       <c r="AZ8" t="n">
-        <v>7.242877836795004e-05</v>
+        <v>0.0003962405256877827</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.001532929379529307</v>
+        <v>0.0001791686574295709</v>
       </c>
       <c r="BB8" t="n">
-        <v>-3.681885125184081e-05</v>
+        <v>0.0006484656447274251</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>9.056439869710998e-05</v>
       </c>
       <c r="BD8" t="n">
         <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0007023910967834613</v>
+        <v>0.0006487512716720379</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.0009022656500497328</v>
+        <v>0.0004907427508355711</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.0001094357976653693</v>
+        <v>0.0006346840560217503</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.0002075215210350839</v>
+        <v>-9.674784451580988e-05</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.004310842484584673</v>
+        <v>0.00199463465806666</v>
       </c>
       <c r="BJ8" t="n">
+        <v>0.0007747708221401445</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.0006029422294636571</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.0001086431675519001</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.0003173464388204816</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0.000587607127912193</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0.001221544215586276</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0.0008404676172892256</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0.002362889490915232</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0.001003177710927764</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0.0002657736747050471</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0.0007608949204555654</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0.0002943371453907661</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0.0006850961694146729</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0.0008048102546539482</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0.0007316575235637307</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>3.647859922178975e-05</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0.0009196782872088166</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>3.980891719743418e-05</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0.0007783235340748651</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0.000313027258318474</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0.0006186895928507157</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0.00131413995699256</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>9.241865364732205e-05</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0.001146374930087474</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>9.043751279775026e-05</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0.0004170074839656729</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>5.152544620689315e-05</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0.0001728770435122318</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>3.980891719744806e-05</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0.0003316639497167956</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0.0003341286464263349</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>8.683031464088443e-05</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>-6.494173588893482e-05</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0.000313571618779504</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>9.131520589714671e-05</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>-1.280081925243148e-05</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>-8.326672684688674e-18</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>3.683693516701448e-05</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0.0003136821007142299</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0.0001318156651741148</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0.0006764422814970917</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>7.166746297184167e-05</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0.0002992832315032556</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0.0006409368808981187</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>0.000301590755715836</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0.0001274863516609215</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0.0003824409710675658</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0.0002354788069073549</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>7.363770250368162e-05</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0.0004244198899636731</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>3.953610964680664e-05</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0.0001840942562592041</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0.0004053259217224353</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0.000325072309644589</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0.0002172863351038001</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF8" t="n">
         <v>3.681885125184081e-05</v>
       </c>
-      <c r="BK8" t="n">
-        <v>0.0001920122887864723</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>3.647859922178975e-05</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>-1.227295041728027e-05</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>-2.454590083456054e-05</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>0.0008488931568114478</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>0.000582863824543603</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>8.887637857591391e-05</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>3.621438918397502e-05</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>0.0002688172043010612</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>-0.0001708681208076046</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>9.056439869714605e-05</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>0.001240246719176238</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>0.0007545147685661725</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>0.000147347740667958</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>0.0002787005987890667</v>
-      </c>
-      <c r="CC8" t="n">
-        <v>8.887637857591391e-05</v>
-      </c>
-      <c r="CD8" t="n">
-        <v>0.001851447554914681</v>
-      </c>
-      <c r="CE8" t="n">
-        <v>0.0005552131290048029</v>
-      </c>
-      <c r="CF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG8" t="n">
-        <v>0.0001704591952407714</v>
-      </c>
-      <c r="CH8" t="n">
-        <v>7.961783439489612e-05</v>
-      </c>
-      <c r="CI8" t="n">
-        <v>0.0007749834194686611</v>
-      </c>
-      <c r="CJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK8" t="n">
-        <v>0.0002502478629969745</v>
-      </c>
-      <c r="CL8" t="n">
-        <v>0.000145914396887159</v>
-      </c>
-      <c r="CM8" t="n">
-        <v>0.0003374934221196724</v>
-      </c>
-      <c r="CN8" t="n">
-        <v>3.647859922178975e-05</v>
-      </c>
-      <c r="CO8" t="n">
-        <v>0.0003364756533375451</v>
-      </c>
-      <c r="CP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ8" t="n">
-        <v>0.0008527201042709709</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>0.0005236960393844553</v>
-      </c>
-      <c r="CS8" t="n">
-        <v>0.000121714776054363</v>
-      </c>
-      <c r="CT8" t="n">
-        <v>0.0001105108055009685</v>
-      </c>
-      <c r="CU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV8" t="n">
-        <v>8.523617683257322e-05</v>
-      </c>
-      <c r="CW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX8" t="n">
-        <v>-4.828585224528892e-05</v>
-      </c>
-      <c r="CY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA8" t="n">
-        <v>0.0001094357976653693</v>
-      </c>
-      <c r="DB8" t="n">
-        <v>0.0001964395423370791</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>0.0004420432220038906</v>
-      </c>
-      <c r="DD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE8" t="n">
-        <v>0.0002222264490686354</v>
-      </c>
-      <c r="DF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG8" t="n">
-        <v>0.0003914285360231723</v>
-      </c>
-      <c r="DH8" t="n">
-        <v>0.001502372166578836</v>
-      </c>
-      <c r="DI8" t="n">
-        <v>0.001112552044229076</v>
-      </c>
-      <c r="DJ8" t="n">
-        <v>0.0004183139724675961</v>
-      </c>
-      <c r="DK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM8" t="n">
-        <v>7.849293563581272e-05</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>-1.280081925243148e-05</v>
-      </c>
-      <c r="DO8" t="n">
-        <v>0.0009352897210175487</v>
-      </c>
-      <c r="DP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX8" t="n">
-        <v>3.683693516697284e-05</v>
-      </c>
-      <c r="DY8" t="n">
-        <v>0.0002304147465437667</v>
-      </c>
-      <c r="DZ8" t="n">
-        <v>5.16956427207449e-05</v>
-      </c>
-      <c r="EA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB8" t="n">
-        <v>0.0005650835880300437</v>
-      </c>
-      <c r="EC8" t="n">
-        <v>0.0007723305465408114</v>
-      </c>
-      <c r="ED8" t="n">
-        <v>0.0001177394034537066</v>
-      </c>
-      <c r="EE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF8" t="n">
-        <v>0.0002881936197698276</v>
-      </c>
       <c r="EG8" t="n">
         <v>0</v>
       </c>
@@ -4432,10 +4432,10 @@
         <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0</v>
+        <v>7.242877836793337e-05</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0</v>
+        <v>0.0002713125383932757</v>
       </c>
       <c r="EK8" t="n">
         <v>0</v>
@@ -4456,7 +4456,7 @@
         <v>0</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>0.0001810719459198334</v>
       </c>
       <c r="ER8" t="n">
         <v>0</v>
@@ -4465,16 +4465,16 @@
         <v>0</v>
       </c>
       <c r="ET8" t="n">
-        <v>0</v>
+        <v>0.0003159717198969625</v>
       </c>
       <c r="EU8" t="n">
-        <v>8.446828222423986e-05</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0001539537926376816</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
         <v>0</v>
@@ -4490,424 +4490,424 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.006694781233526658</v>
+        <v>0.001857749469214431</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0006322957198443557</v>
+        <v>0.0002454590083456054</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005160057333970358</v>
+        <v>0.000627716079188756</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002741170268845561</v>
+        <v>0.0006688963210703224</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0003162888771745198</v>
+        <v>0.0005232862375719072</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00261643118785978</v>
+        <v>0.003822264691829968</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0005756148613291878</v>
+        <v>0.002721088435374097</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002070063694267488</v>
+        <v>0.002016985138004212</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004989384288747322</v>
+        <v>0.00116772823779191</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0007858546168958314</v>
+        <v>0.0001024065540194741</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0003438113948919241</v>
+        <v>0.0003344481605351612</v>
       </c>
       <c r="M9" t="n">
-        <v>0.004682274247491613</v>
+        <v>0.004322200392927333</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0002431906614785984</v>
+        <v>0.002110817941952547</v>
       </c>
       <c r="O9" t="n">
-        <v>0.004164470216130767</v>
+        <v>0.004511677282377891</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0005255613951265948</v>
+        <v>0.0005277044854881563</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.00668789808917195</v>
+        <v>0.005808477237048626</v>
       </c>
       <c r="R9" t="n">
-        <v>0.000896151818661084</v>
+        <v>0.002760084925689987</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002741170268845583</v>
+        <v>0.002704007725736313</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0008349705304518396</v>
+        <v>0.0003380009657170224</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001620825147347715</v>
+        <v>0.0005255613951266724</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003781925343811376</v>
+        <v>0.00530785562632693</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0009023354564755559</v>
+        <v>0.004643799472295551</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01371237458193978</v>
+        <v>0.00922121356903971</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0003715498938428596</v>
+        <v>0.0001911132345915334</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.00520783564261823</v>
+        <v>0.0169135212613474</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.007262302914476803</v>
+        <v>0.007931199235547115</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0004300047778308502</v>
+        <v>0.0006900212314224774</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.001894521249359948</v>
+        <v>0.0002414292612264335</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.02704252269469659</v>
+        <v>0.006114918292040039</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.01868131868131865</v>
+        <v>0.01100196463654228</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.003045186640471498</v>
+        <v>0.004749340369393206</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0006381934216985741</v>
+        <v>0.001674515960230216</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0007242877836794448</v>
+        <v>0.001360544217687054</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.005376910911966304</v>
+        <v>0.001958910654562862</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.01331041257367385</v>
+        <v>0.004469548133595324</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0519350215002389</v>
+        <v>0.05728619206880081</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.001767797419971317</v>
+        <v>0.0004777070063693878</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0153368370759675</v>
+        <v>0.007692307692307665</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.004375329467580413</v>
+        <v>0.001220806794055163</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.006114918292040106</v>
+        <v>0.002914476827520351</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0008372579801151691</v>
+        <v>0.0009657170449058006</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.004955192409066988</v>
+        <v>0.002866242038216538</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.01964636542239683</v>
+        <v>0.008706225680933899</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.001686874011597295</v>
+        <v>0.0003184713375795955</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.001804670912951145</v>
+        <v>0.007961783439490434</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.002319451765946257</v>
+        <v>0.0009554140127388311</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.004299363057324812</v>
+        <v>0.001158860453886945</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.003268318397469716</v>
+        <v>0.0009728622631849038</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.000764452938365956</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.001653696498054469</v>
+        <v>0.003440038222646968</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.001070038910505833</v>
+        <v>0.0006688963210703003</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.002285992217898825</v>
+        <v>0.0007295719844357951</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.002626459143968862</v>
+        <v>0.00185774946921442</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0005255613951265948</v>
+        <v>0.0002866698518873001</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.000540275049115857</v>
+        <v>0.0002123142250530563</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.01544585987261143</v>
+        <v>0.002091439688715946</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.010244161358811</v>
+        <v>0.005573248407643283</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.001831501831501847</v>
+        <v>0.003715498938428852</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.001528729573010068</v>
+        <v>0.0005838641188959271</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.01119832548403982</v>
+        <v>0.007012035583464127</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.00164543524416132</v>
+        <v>0.002532981530343037</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.00305745914602007</v>
+        <v>0.001804670912951134</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0005838641188959492</v>
+        <v>0.0003344481605351834</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0001964636542239329</v>
+        <v>0.000768049155146</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.002229299363057291</v>
+        <v>0.003025477707006341</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.000386286817962378</v>
+        <v>0.002176220806794027</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.001620825147347715</v>
+        <v>0.004777070063694244</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.004156712852365007</v>
+        <v>0.006953290870488293</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.001465201465201504</v>
+        <v>0.002093144950287762</v>
       </c>
       <c r="BT9" t="n">
+        <v>0.001528905876732023</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.001792303637322057</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.001114649681528645</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0.001146679407549023</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0.002962255136168201</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.003573153066151569</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0.001433349259436267</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0.005679405520169822</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.0006802721088435048</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.002704007725736301</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.001994163424124507</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.001337792642140534</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.001910828025477684</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.002150023889154373</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.001720019111323512</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0.001910828025477696</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0.001255886970172648</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0.0005232862375719183</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0.0003162888771744754</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0.001290014333492651</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.0009174311926604895</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.001786576533075757</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.002511773940345341</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0.001046572475143881</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0.00151753008895863</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0.0002897151134717335</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>9.823182711199419e-05</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.004709576138147531</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>5.307855626326408e-05</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.0002123142250530563</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0.0005733397037745447</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0.001098901098901073</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0.0001473477406680024</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>9.657170449057783e-05</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0.0004749340369393007</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0.001423299947285139</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.005637840420449148</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.001958910654562873</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0.002335456475583841</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0.002388535031847105</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0.002866242038216538</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0.0008443271767810456</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>0.001481127568084162</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0.001831501831501803</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.0001061571125265171</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>0.00014333492594365</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.0005271481286240887</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0.003819989534275203</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0.0006852925672113485</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>5.232862375719183e-05</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.000579430226943467</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>0.003248924988055457</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.0005733397037745669</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.0019884877027734</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0.005781175346392786</v>
+      </c>
+      <c r="EC9" t="n">
         <v>0.0008268482490272344</v>
       </c>
-      <c r="BU9" t="n">
-        <v>0.004193205944798284</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>0.0001024065540194519</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>0.001380042462844988</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>0.004375329467580435</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>0.003874734607218644</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0.001167315175097272</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>0.00260314341846758</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>0.0008840864440078256</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>0.006163401815575708</v>
-      </c>
-      <c r="CE9" t="n">
-        <v>0.002616431187859791</v>
-      </c>
-      <c r="CF9" t="n">
-        <v>0.001719056974459687</v>
-      </c>
-      <c r="CG9" t="n">
-        <v>0.00153927813163478</v>
-      </c>
-      <c r="CH9" t="n">
-        <v>0.006736741519350197</v>
-      </c>
-      <c r="CI9" t="n">
-        <v>0.00506450071667458</v>
-      </c>
-      <c r="CJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>0.001911132345914934</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>0.003110173958882479</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>0.003584607274644202</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>0.005494505494505475</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>0.0007961783439490167</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>5.271481286241997e-05</v>
-      </c>
-      <c r="CQ9" t="n">
-        <v>0.006167633104902514</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>0.001051122790253223</v>
-      </c>
-      <c r="CS9" t="n">
-        <v>0.002006688963210679</v>
-      </c>
-      <c r="CT9" t="n">
-        <v>0.0008895866038723388</v>
-      </c>
-      <c r="CU9" t="n">
-        <v>0.0003404669260700377</v>
-      </c>
-      <c r="CV9" t="n">
-        <v>0.001008492569002117</v>
-      </c>
-      <c r="CW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX9" t="n">
-        <v>0.000294695481335927</v>
-      </c>
-      <c r="CY9" t="n">
-        <v>0.001719056974459676</v>
-      </c>
-      <c r="CZ9" t="n">
-        <v>0.0002431906614785984</v>
-      </c>
-      <c r="DA9" t="n">
-        <v>0.0005255613951265948</v>
-      </c>
-      <c r="DB9" t="n">
-        <v>0.004156712852365019</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>0.002054467271858562</v>
-      </c>
-      <c r="DD9" t="n">
-        <v>0.0004246284501061126</v>
-      </c>
-      <c r="DE9" t="n">
-        <v>0.003296703296703274</v>
-      </c>
-      <c r="DF9" t="n">
-        <v>0.001313229571984431</v>
-      </c>
-      <c r="DG9" t="n">
-        <v>0.004428044280442833</v>
-      </c>
-      <c r="DH9" t="n">
-        <v>0.01299569995222168</v>
-      </c>
-      <c r="DI9" t="n">
-        <v>0.004638903531892491</v>
-      </c>
-      <c r="DJ9" t="n">
-        <v>0.00095541401273882</v>
-      </c>
-      <c r="DK9" t="n">
-        <v>0.001326129666011766</v>
-      </c>
-      <c r="DL9" t="n">
-        <v>9.727626459143934e-05</v>
-      </c>
-      <c r="DM9" t="n">
-        <v>0.0007858546168958425</v>
-      </c>
-      <c r="DN9" t="n">
-        <v>0.006211180124223581</v>
-      </c>
-      <c r="DO9" t="n">
-        <v>0.006642066420664261</v>
-      </c>
-      <c r="DP9" t="n">
-        <v>0.0111323459149546</v>
-      </c>
-      <c r="DQ9" t="n">
-        <v>0.0001448575567359001</v>
-      </c>
-      <c r="DR9" t="n">
-        <v>0.00100158144438588</v>
-      </c>
-      <c r="DS9" t="n">
-        <v>0.0004744333157617797</v>
-      </c>
-      <c r="DT9" t="n">
-        <v>0.00152259332023571</v>
-      </c>
-      <c r="DU9" t="n">
-        <v>0.006800210859251477</v>
-      </c>
-      <c r="DV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW9" t="n">
-        <v>0.0004186289900576012</v>
-      </c>
-      <c r="DX9" t="n">
-        <v>0.0004608294930875334</v>
-      </c>
-      <c r="DY9" t="n">
-        <v>0.002741170268845583</v>
-      </c>
-      <c r="DZ9" t="n">
-        <v>0.0007326007326007633</v>
-      </c>
-      <c r="EA9" t="n">
-        <v>4.828585224530002e-05</v>
-      </c>
-      <c r="EB9" t="n">
-        <v>0.003535594839942658</v>
-      </c>
-      <c r="EC9" t="n">
-        <v>0.006593406593406603</v>
-      </c>
       <c r="ED9" t="n">
-        <v>0.001863354037267062</v>
+        <v>0.002760084925689987</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0003929273084478879</v>
+        <v>0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.001273885350318449</v>
+        <v>0.002123142250530752</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.000955566172957456</v>
+        <v>0.0005733397037745447</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0003139717425432065</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.002123142250530752</v>
+        <v>0.001255886970172659</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0006369426751592133</v>
+        <v>0.001698513800424595</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.00145914396887159</v>
+        <v>0.0001473477406679913</v>
       </c>
       <c r="EL9" t="n">
         <v>0</v>
@@ -4916,40 +4916,40 @@
         <v>0</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.00057561486132921</v>
+        <v>9.657170449057783e-05</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.0001061571125265282</v>
+        <v>0.000530785562632674</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0001433349259436167</v>
+        <v>0.001486199575371527</v>
       </c>
       <c r="ER9" t="n">
-        <v>9.657170449060005e-05</v>
+        <v>0</v>
       </c>
       <c r="ES9" t="n">
-        <v>9.727626459143934e-05</v>
+        <v>0</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.005113336847654226</v>
+        <v>0.003078556263269605</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.0005836575875486361</v>
+        <v>5.307855626325297e-05</v>
       </c>
       <c r="EV9" t="n">
-        <v>0</v>
+        <v>0.0003690036900368621</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0005402750491158681</v>
+        <v>0.001804670912951134</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.000291828793774318</v>
+        <v>0.002441613588110369</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0002123142250530563</v>
+        <v>0.000145914396887159</v>
       </c>
     </row>
   </sheetData>
